--- a/EDRMS_Dashboard_Contents_2026-08-17.xlsx
+++ b/EDRMS_Dashboard_Contents_2026-08-17.xlsx
@@ -74,7 +74,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +109,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9E2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,13 +190,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -2471,16 +2476,36 @@
           <t>Documents</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr"/>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>One document held by this unit.</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Sum the document count over the unit's sites.</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="10" t="n">
@@ -2547,15 +2572,31 @@
           <t>Share of documents</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
-      <c r="I39" s="10" t="inlineStr"/>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>This unit's documents divided by all documents, times 100.</t>
+        </is>
+      </c>
       <c r="J39" s="10" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -2653,18 +2694,38 @@
           <t>Share of documents declared as records</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr"/>
-      <c r="F42" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr"/>
-      <c r="H42" s="10" t="inlineStr"/>
-      <c r="I42" s="10" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>A RATE: declared records over ALL documents held. Reads about 0.62%, which looks like a fault and is not.</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records" and the weekly scan</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Declared records divided by documents held, times 100.</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>The denominator does not exist yet: public."Records" holds no row for an undeclared document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
       <c r="A43" s="10" t="n">
         <v>42</v>
       </c>
@@ -2683,16 +2744,38 @@
           <t>Departments with zero declarations</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr"/>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>One organisational unit that owns EDRMS sites but has declared nothing.</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report and drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>1. List every unit in the compliant site list.
+2. Subtract the units that appear in Records.
+3. Count what is left.</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>This is a compliance finding worth reporting: a site designated EDRMS that nobody uses.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="10" t="n">
@@ -2912,7 +2995,7 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>A RATE, not a count: declared records over documents held, for the same unit.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -2932,12 +3015,12 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Records declared divided by documents held, per unit.</t>
+          <t>Declared records divided by documents held, per unit.</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>The denominator does not exist in any system yet. public."Records" holds NO ROW for an undeclared document, so every rate waits on the scan.</t>
+          <t>Waits on the scan for the denominator.</t>
         </is>
       </c>
     </row>
@@ -2960,15 +3043,31 @@
           <t>Share of records</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr"/>
-      <c r="H49" s="10" t="inlineStr"/>
-      <c r="I49" s="10" t="inlineStr"/>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>This unit's declared records divided by all declared records, times 100.</t>
+        </is>
+      </c>
       <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
@@ -3066,15 +3165,31 @@
           <t>Share of declared records</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr"/>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr"/>
-      <c r="H52" s="10" t="inlineStr"/>
-      <c r="I52" s="10" t="inlineStr"/>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Physical counterparts divided by declared records, times 100.</t>
+        </is>
+      </c>
       <c r="J52" s="10" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
@@ -3331,15 +3446,31 @@
           <t>Share with counterpart</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr"/>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr"/>
-      <c r="H58" s="10" t="inlineStr"/>
-      <c r="I58" s="10" t="inlineStr"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Records with a counterpart divided by records declared, times 100.</t>
+        </is>
+      </c>
       <c r="J58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
@@ -3391,16 +3522,36 @@
           <t>Due within 30 days</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr"/>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr"/>
-      <c r="H60" s="10" t="inlineStr"/>
-      <c r="I60" s="10" t="inlineStr"/>
-      <c r="J60" s="10" t="inlineStr"/>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>One record whose disposal date falls in the next 30 days.</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Count records due between now and now + 30 days.</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>The three windows must nest: 30 inside 90 inside 12 months.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="10" t="n">
@@ -3421,15 +3572,31 @@
           <t>Due within 90 days</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr"/>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr"/>
-      <c r="H61" s="10" t="inlineStr"/>
-      <c r="I61" s="10" t="inlineStr"/>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the next 90 days.</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Count records due between now and now + 90 days.</t>
+        </is>
+      </c>
       <c r="J61" s="10" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
@@ -3451,15 +3618,31 @@
           <t>Due within 12 months</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr"/>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr"/>
-      <c r="H62" s="10" t="inlineStr"/>
-      <c r="I62" s="10" t="inlineStr"/>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the next 12 months.</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Count records due between now and now + 12 months.</t>
+        </is>
+      </c>
       <c r="J62" s="10" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
@@ -3869,16 +4052,36 @@
           <t>Total number of sites created</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS site owned by this unit.</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS Site Type, Department</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Count compliant sites for the unit.</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Same multi-department problem. Audit question 1.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="n">
@@ -3899,16 +4102,36 @@
           <t>Total number of EDRMS users</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>One person with access to this unit's EDRMS sites.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint activity user detail (M365)</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>User Principal Name</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct users with activity, for this unit.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>The activity report has NO SITE DIMENSION, so it cannot be narrowed to EDRMS. 1,028 of 1,032 EDRMS sites are Team sites with no M365 group, so group membership reaches almost nothing either. Untested route: read role assignments per site. Audit question 3.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="10" t="n">
@@ -3929,16 +4152,36 @@
           <t>Total number of site visitors</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>One PERSON who opened a site in this unit.</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph site analytics</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>actorCount</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Sum actorCount over the unit's sites.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Graph offers allTime and lastSevenDays only. No 30 day unique viewer figure exists.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="10" t="n">
@@ -4189,16 +4432,36 @@
           <t>Total number of sites created</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS site owned by this unit.</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS Site Type, Department</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Count compliant sites for the unit.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Same multi-department problem. Audit question 1.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="10" t="n">
@@ -4515,16 +4778,36 @@
           <t>Number of documents</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>One document held by this site.</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Count documents in the site's libraries.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -4545,15 +4828,31 @@
           <t>Number of records</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>One declared record.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>ListId, ItemId</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records"</t>
+        </is>
+      </c>
       <c r="J22" s="10" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -4575,15 +4874,31 @@
           <t>Number of physical counterparts</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
       <c r="J23" s="10" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -4605,15 +4920,31 @@
           <t>Number of records due for disposal</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the window.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
       <c r="J24" s="10" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -4638,7 +4969,7 @@
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr"/>
@@ -4668,7 +4999,7 @@
       <c r="E26" s="10" t="inlineStr"/>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr"/>
@@ -4875,10 +5206,14 @@
           <t>Activity</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>An activity band, not a measure: the row label for the users table.</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr"/>
@@ -4905,16 +5240,36 @@
           <t>Number of users</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>One person in this activity band.</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint activity user detail (M365)</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Last Activity Date</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Count users falling in the band.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Needs the user to department mapping. Audit question 3.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="10" t="n">
@@ -4935,15 +5290,31 @@
           <t>Share of department</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
       <c r="J33" s="10" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1">
@@ -4968,7 +5339,7 @@
       <c r="E34" s="10" t="inlineStr"/>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr"/>
@@ -4998,7 +5369,7 @@
       <c r="E35" s="10" t="inlineStr"/>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -5028,7 +5399,7 @@
       <c r="E36" s="10" t="inlineStr"/>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr"/>
@@ -5185,15 +5556,31 @@
           <t>Sites reporting</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr"/>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr"/>
-      <c r="H40" s="10" t="inlineStr"/>
-      <c r="I40" s="10" t="inlineStr"/>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>One site that appears in this table.</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS Site Type</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Count the rows in the table.</t>
+        </is>
+      </c>
       <c r="J40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -5411,15 +5798,31 @@
           <t>Share of department</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr"/>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
-      <c r="I45" s="10" t="inlineStr"/>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
       <c r="J45" s="10" t="inlineStr"/>
     </row>
     <row r="46" ht="48" customHeight="1">
@@ -5544,16 +5947,36 @@
           <t>Total documents size</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr"/>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr"/>
-      <c r="H48" s="10" t="inlineStr"/>
-      <c r="I48" s="10" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr"/>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Bytes held by this unit's documents.</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Storage Used (GB)</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Sum Storage Used (GB) over the unit's sites.</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Never inferred from a document count.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="n">
@@ -5574,15 +5997,31 @@
           <t>Sites reporting</t>
         </is>
       </c>
-      <c r="E49" s="10" t="inlineStr"/>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr"/>
-      <c r="H49" s="10" t="inlineStr"/>
-      <c r="I49" s="10" t="inlineStr"/>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>One site that appears in this table.</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS Site Type</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Count the rows in the table.</t>
+        </is>
+      </c>
       <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
@@ -5650,16 +6089,36 @@
           <t>Number of documents created / uploaded</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr"/>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr"/>
-      <c r="I51" s="10" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>One document created or uploaded here.</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Count documents per site.</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Nothing marks a document as MIGRATED, so migrated counts cannot be split out. Question 9.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="10" t="n">
@@ -5680,16 +6139,36 @@
           <t>Number of users creating documents</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr"/>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr"/>
-      <c r="H52" s="10" t="inlineStr"/>
-      <c r="I52" s="10" t="inlineStr"/>
-      <c r="J52" s="10" t="inlineStr"/>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>One person who created a document here.</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct document authors per site.</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="10" t="n">
@@ -5710,15 +6189,31 @@
           <t>Documents size (in GB)</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr"/>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr"/>
-      <c r="H53" s="10" t="inlineStr"/>
-      <c r="I53" s="10" t="inlineStr"/>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Bytes held by this site.</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Storage Used (GB)</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Read Storage Used (GB) per site.</t>
+        </is>
+      </c>
       <c r="J53" s="10" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customHeight="1">
@@ -5743,7 +6238,7 @@
       <c r="E54" s="10" t="inlineStr"/>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr"/>
@@ -5852,16 +6347,36 @@
           <t>Total number of users declaring records</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr"/>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr"/>
-      <c r="H57" s="10" t="inlineStr"/>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>One person who declared at least one record here.</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>One line of SQL that has never been run.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="10" t="n">
@@ -5882,16 +6397,36 @@
           <t>Total declared record size</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr"/>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr"/>
-      <c r="H58" s="10" t="inlineStr"/>
-      <c r="I58" s="10" t="inlineStr"/>
-      <c r="J58" s="10" t="inlineStr"/>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Bytes held by the declared records specifically.</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>FileSize</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Sum FileSize over the documents that appear in Records.</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>Graph returns a CUMULATIVE size on folders, so the scan must filter to files only or storage is double counted.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="10" t="n">
@@ -5912,16 +6447,36 @@
           <t>Sites with no declared record in 90 days</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr"/>
-      <c r="H59" s="10" t="inlineStr"/>
-      <c r="I59" s="10" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr"/>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS site whose most recent declaration is older than 90 days.</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl, CreatedDate</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>MAX(CreatedDate) per SiteUrl, count the sites where it is older than 90 days.</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>A compliance finding: a site designated EDRMS that has stopped being used.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="10" t="n">
@@ -6092,7 +6647,7 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>A RATE, not a count: declared records over documents held, for the same unit.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
@@ -6112,12 +6667,12 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Records declared divided by documents held, per unit.</t>
+          <t>Declared records divided by documents held, per unit.</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>The denominator does not exist in any system yet. public."Records" holds NO ROW for an undeclared document, so every rate waits on the scan.</t>
+          <t>Waits on the scan for the denominator.</t>
         </is>
       </c>
     </row>
@@ -6140,15 +6695,31 @@
           <t>Share of department</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr"/>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr"/>
-      <c r="H64" s="10" t="inlineStr"/>
-      <c r="I64" s="10" t="inlineStr"/>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
       <c r="J64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
@@ -6173,7 +6744,7 @@
       <c r="E65" s="10" t="inlineStr"/>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr"/>
@@ -6200,16 +6771,36 @@
           <t>Sites with no declared record in 90 days</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr"/>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr"/>
-      <c r="H66" s="10" t="inlineStr"/>
-      <c r="I66" s="10" t="inlineStr"/>
-      <c r="J66" s="10" t="inlineStr"/>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS site whose most recent declaration is older than 90 days.</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl, CreatedDate</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>MAX(CreatedDate) per SiteUrl, count the sites where it is older than 90 days.</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>A compliance finding: a site designated EDRMS that has stopped being used.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="10" t="n">
@@ -6260,15 +6851,31 @@
           <t>Total number of physical records declared</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr"/>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr"/>
-      <c r="H68" s="10" t="inlineStr"/>
-      <c r="I68" s="10" t="inlineStr"/>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical, per site.</t>
+        </is>
+      </c>
       <c r="J68" s="10" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -6290,16 +6897,36 @@
           <t>Total number of users declaring records</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr"/>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr"/>
-      <c r="H69" s="10" t="inlineStr"/>
-      <c r="I69" s="10" t="inlineStr"/>
-      <c r="J69" s="10" t="inlineStr"/>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>One person who declared at least one record here.</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>One line of SQL that has never been run.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="10" t="n">
@@ -6320,15 +6947,31 @@
           <t>Share of declared records</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr"/>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr"/>
-      <c r="H70" s="10" t="inlineStr"/>
-      <c r="I70" s="10" t="inlineStr"/>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Physical counterparts divided by declared records, times 100.</t>
+        </is>
+      </c>
       <c r="J70" s="10" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -6350,15 +6993,31 @@
           <t>Sites reporting</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr"/>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr"/>
-      <c r="H71" s="10" t="inlineStr"/>
-      <c r="I71" s="10" t="inlineStr"/>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>One site that appears in this table.</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>EDRMS Site Type</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Count the rows in the table.</t>
+        </is>
+      </c>
       <c r="J71" s="10" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
@@ -6426,15 +7085,31 @@
           <t>Total number of physical records declared</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr"/>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr"/>
-      <c r="H73" s="10" t="inlineStr"/>
-      <c r="I73" s="10" t="inlineStr"/>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical, per site.</t>
+        </is>
+      </c>
       <c r="J73" s="10" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
@@ -6456,16 +7131,36 @@
           <t>Total number of users declaring records</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr"/>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr"/>
-      <c r="H74" s="10" t="inlineStr"/>
-      <c r="I74" s="10" t="inlineStr"/>
-      <c r="J74" s="10" t="inlineStr"/>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>One person who declared at least one record here.</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>One line of SQL that has never been run.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="10" t="n">
@@ -6486,15 +7181,31 @@
           <t>Share with a counterpart</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr"/>
-      <c r="H75" s="10" t="inlineStr"/>
-      <c r="I75" s="10" t="inlineStr"/>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Records with a counterpart divided by records declared, times 100.</t>
+        </is>
+      </c>
       <c r="J75" s="10" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
@@ -6516,15 +7227,31 @@
           <t>Share of department</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr"/>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr"/>
-      <c r="H76" s="10" t="inlineStr"/>
-      <c r="I76" s="10" t="inlineStr"/>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
       <c r="J76" s="10" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
@@ -6549,7 +7276,7 @@
       <c r="E77" s="10" t="inlineStr"/>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr"/>
@@ -6579,7 +7306,7 @@
       <c r="E78" s="10" t="inlineStr"/>
       <c r="F78" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr"/>
@@ -6687,15 +7414,31 @@
           <t>Libraries with records due</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr"/>
-      <c r="F81" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr"/>
-      <c r="H81" s="10" t="inlineStr"/>
-      <c r="I81" s="10" t="inlineStr"/>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>One library holding at least one record due for disposal.</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>ListId, EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct ListId among records due.</t>
+        </is>
+      </c>
       <c r="J81" s="10" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1">
@@ -6717,16 +7460,36 @@
           <t>Library name</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr"/>
-      <c r="F82" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr"/>
-      <c r="H82" s="10" t="inlineStr"/>
-      <c r="I82" s="10" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr"/>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>One document library inside an EDRMS site.</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>drives, list.id</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>GET /sites/{siteId}/drives. list.id is the ListId key that joins to Records.</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>Always show a library with its parent site: display names repeat across sites.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="10" t="n">
@@ -6747,15 +7510,31 @@
           <t>Number of records due for disposal</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr"/>
-      <c r="H83" s="10" t="inlineStr"/>
-      <c r="I83" s="10" t="inlineStr"/>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the window.</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
       <c r="J83" s="10" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
@@ -6777,15 +7556,31 @@
           <t>Next due date for disposal</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr"/>
-      <c r="F84" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr"/>
-      <c r="H84" s="10" t="inlineStr"/>
-      <c r="I84" s="10" t="inlineStr"/>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>The earliest disposal date still ahead for this library.</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>MIN(EDRMSDueDateForDisposal) in the future, per ListId.</t>
+        </is>
+      </c>
       <c r="J84" s="10" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
@@ -6807,15 +7602,31 @@
           <t>With physical counterpart?</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr"/>
-      <c r="H85" s="10" t="inlineStr"/>
-      <c r="I85" s="10" t="inlineStr"/>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Whether the records due here include paper originals.</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Any HasPhysical among the library's records due.</t>
+        </is>
+      </c>
       <c r="J85" s="10" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
@@ -6837,15 +7648,31 @@
           <t>Share of department</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr"/>
-      <c r="F86" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr"/>
-      <c r="H86" s="10" t="inlineStr"/>
-      <c r="I86" s="10" t="inlineStr"/>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
       <c r="J86" s="10" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
@@ -6870,7 +7697,7 @@
       <c r="E87" s="10" t="inlineStr"/>
       <c r="F87" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr"/>
@@ -6900,7 +7727,7 @@
       <c r="E88" s="10" t="inlineStr"/>
       <c r="F88" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr"/>
@@ -6930,7 +7757,7 @@
       <c r="E89" s="10" t="inlineStr"/>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr"/>
@@ -6960,7 +7787,7 @@
       <c r="E90" s="10" t="inlineStr"/>
       <c r="F90" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr"/>
@@ -7156,16 +7983,24 @@
           <t>Total terms</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term.</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
       <c r="H5" s="10" t="inlineStr"/>
       <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Audit question 12.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="n">
@@ -7186,16 +8021,24 @@
           <t>Total Institutional Management terms</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term under the Institutional Management category.</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither system. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="n">
@@ -7216,16 +8059,24 @@
           <t>Total Administration terms</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term under the Administration category.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither system. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="10" t="n">
@@ -7246,16 +8097,24 @@
           <t>Total People Management terms</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term under the People Management category.</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="10" t="inlineStr"/>
       <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither system. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="n">
@@ -7276,16 +8135,24 @@
           <t>Total Programs and Operations terms</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term under the Programs and Operations category.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
       <c r="H9" s="10" t="inlineStr"/>
       <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither system. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="10" t="n">
@@ -7306,16 +8173,24 @@
           <t>Total Other terms</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term under the Other category.</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither system. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="n">
@@ -7396,10 +8271,14 @@
           <t>Heading</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>A column of row labels, not a measure.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -7426,16 +8305,24 @@
           <t>Total terms</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>One file plan term.</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="10" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Audit question 12.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="n">
@@ -7456,15 +8343,31 @@
           <t>Departments, offices and RMs provisioned</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>One organisational unit represented here.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct Department.</t>
+        </is>
+      </c>
       <c r="J15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -7486,15 +8389,31 @@
           <t>Number of libraries provisioned</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>One document library.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>drives</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Count libraries per site, summed for the unit.</t>
+        </is>
+      </c>
       <c r="J16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -7516,16 +8435,36 @@
           <t>Number of documents</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>One document held by this site.</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Count documents in the site's libraries.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="10" t="n">
@@ -7546,15 +8485,31 @@
           <t>Number of records declared</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this site.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records" GROUP BY "SiteUrl"</t>
+        </is>
+      </c>
       <c r="J18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -7576,15 +8531,31 @@
           <t>Number of physical counterparts</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
       <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -7636,16 +8607,24 @@
           <t>Total terms (top level)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>One top level file plan term.</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Audit question 12.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -7666,15 +8645,31 @@
           <t>Total number of libraries provisioned</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>One document library across EDRMS sites.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>drives</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>GET /sites/{siteId}/drives per compliant site, count the libraries.</t>
+        </is>
+      </c>
       <c r="J22" s="10" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -7844,16 +8839,24 @@
           <t>Term (top level)</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>One top level institutional file plan term.</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither the term store nor Purview. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="10" t="n">
@@ -7874,15 +8877,31 @@
           <t>Departments, offices and RMs provisioned</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>One organisational unit represented here.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct Department.</t>
+        </is>
+      </c>
       <c r="J27" s="10" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -7904,15 +8923,31 @@
           <t>Number of libraries provisioned</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr"/>
-      <c r="I28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>One document library.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>drives</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Count libraries per site, summed for the unit.</t>
+        </is>
+      </c>
       <c r="J28" s="10" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
@@ -7934,16 +8969,36 @@
           <t>Number of documents</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>One document held by this site.</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Count documents in the site's libraries.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="10" t="n">
@@ -7964,15 +9019,31 @@
           <t>Number of records declared</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this site.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records" GROUP BY "SiteUrl"</t>
+        </is>
+      </c>
       <c r="J30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -7994,15 +9065,31 @@
           <t>Number of physical counterparts</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
       <c r="J31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -8027,7 +9114,7 @@
       <c r="E32" s="10" t="inlineStr"/>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr"/>
@@ -8057,7 +9144,7 @@
       <c r="E33" s="10" t="inlineStr"/>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr"/>
@@ -8087,7 +9174,7 @@
       <c r="E34" s="10" t="inlineStr"/>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr"/>
@@ -8117,7 +9204,7 @@
       <c r="E35" s="10" t="inlineStr"/>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -8373,10 +9460,14 @@
           <t>Heading</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>A column of row labels, not a measure.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -8403,15 +9494,31 @@
           <t>Departments, offices and RMs provisioned</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>One organisational unit represented here.</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct Department.</t>
+        </is>
+      </c>
       <c r="J8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -8433,15 +9540,31 @@
           <t>Number of libraries provisioned</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>One document library.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>drives</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Count libraries per site, summed for the unit.</t>
+        </is>
+      </c>
       <c r="J9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -8463,15 +9586,31 @@
           <t>Number of records declared</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this site.</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records" GROUP BY "SiteUrl"</t>
+        </is>
+      </c>
       <c r="J10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -8493,15 +9632,31 @@
           <t>Number of physical counterparts</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
       <c r="J11" s="10" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -8523,15 +9678,31 @@
           <t>Number of records due for disposal</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the window.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
       <c r="J12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -8583,16 +9754,24 @@
           <t>Term (top level)</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>One top level institutional file plan term.</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="10" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither the term store nor Purview. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="n">
@@ -8613,15 +9792,31 @@
           <t>Departments, offices and RMs provisioned</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>One organisational unit represented here.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct Department.</t>
+        </is>
+      </c>
       <c r="J15" s="10" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -8643,15 +9838,31 @@
           <t>Number of libraries provisioned</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>One document library.</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>drives</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Count libraries per site, summed for the unit.</t>
+        </is>
+      </c>
       <c r="J16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -8673,16 +9884,36 @@
           <t>Number of documents</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>One document held by this site.</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Count documents in the site's libraries.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="10" t="n">
@@ -8703,15 +9934,31 @@
           <t>Number of records declared</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this site.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records" GROUP BY "SiteUrl"</t>
+        </is>
+      </c>
       <c r="J18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -8733,15 +9980,31 @@
           <t>Number of physical counterparts</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
       <c r="J19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -8793,16 +10056,24 @@
           <t>Term (top level)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>One top level institutional file plan term.</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>The file plan exists in neither the term store nor Purview. Audit questions 12 and 13.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="10" t="n">
@@ -8823,15 +10094,31 @@
           <t>Departments, offices and RMs provisioned</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>One organisational unit represented here.</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Count distinct Department.</t>
+        </is>
+      </c>
       <c r="J22" s="10" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -8853,15 +10140,31 @@
           <t>Number of libraries provisioned</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>One document library.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>drives</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Count libraries per site, summed for the unit.</t>
+        </is>
+      </c>
       <c r="J23" s="10" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -8883,15 +10186,31 @@
           <t>Number of records declared</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this site.</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records" GROUP BY "SiteUrl"</t>
+        </is>
+      </c>
       <c r="J24" s="10" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -8913,15 +10232,31 @@
           <t>Number of physical counterparts</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
       <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -8943,16 +10278,36 @@
           <t>Retention label</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>One Purview retention label applied to records.</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Purview, Records management, File plan</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Label name</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Read the label per record from the document row.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>53 labels in the test tenant, a FLAT list with no hierarchy.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="10" t="n">
@@ -8973,15 +10328,31 @@
           <t>Number of records due for disposal</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the window.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
       <c r="J27" s="10" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -9033,16 +10404,36 @@
           <t>Retention label</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>One Purview retention label applied to records.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Purview, Records management, File plan</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Label name</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Read the label per record from the document row.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>53 labels in the test tenant, a FLAT list with no hierarchy.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="10" t="n">
@@ -9063,15 +10454,31 @@
           <t>Number of records declared</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this site.</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records" GROUP BY "SiteUrl"</t>
+        </is>
+      </c>
       <c r="J30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -9093,15 +10500,31 @@
           <t>Share of declared records</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Physical counterparts divided by declared records, times 100.</t>
+        </is>
+      </c>
       <c r="J31" s="10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -9308,16 +10731,36 @@
           <t>Physical counterparts identified</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>One declared record that also exists on paper.</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM public."Records" WHERE "HasPhysical" IS TRUE</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>The one figure on this dashboard that has a source. It is the bridge between this report and the physical estate, which is why it is the only KPI card kept here. Everything else on Records and Archive Holdings has no source at all, audit question 17.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="n">
@@ -9401,7 +10844,7 @@
       <c r="E8" s="10" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
@@ -9431,7 +10874,7 @@
       <c r="E9" s="10" t="inlineStr"/>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -9461,7 +10904,7 @@
       <c r="E10" s="10" t="inlineStr"/>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr"/>
@@ -9491,7 +10934,7 @@
       <c r="E11" s="10" t="inlineStr"/>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr"/>
@@ -9551,7 +10994,7 @@
       <c r="E13" s="10" t="inlineStr"/>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -9581,7 +11024,7 @@
       <c r="E14" s="10" t="inlineStr"/>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
@@ -9611,7 +11054,7 @@
       <c r="E15" s="10" t="inlineStr"/>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -9641,7 +11084,7 @@
       <c r="E16" s="10" t="inlineStr"/>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr"/>
@@ -9703,7 +11146,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -9713,7 +11156,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -9723,17 +11166,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Asked for, not built</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -9743,7 +11186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">

--- a/EDRMS_Dashboard_Contents_2026-08-17.xlsx
+++ b/EDRMS_Dashboard_Contents_2026-08-17.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>TWO problems. (a) The export has NO SITE DIMENSION, so it cannot be narrowed to EDRMS: at ADB it returns every licensed user, about 9,400. (b) 180 days is the longest period Microsoft serves, so a user last active 200 days ago is indistinguishable from one who never used EDRMS. Audit questions 3 and 16.</t>
+          <t>TWO problems. (a) NO SITE DIMENSION. Counted 17 Aug: the export has 12 columns and not one of them names a site, so the row cannot be narrowed to EDRMS and at ADB it returns every licensed user, about 9,400. The obvious fix, join user to site then site to department, CANNOT BE BUILT from any export we hold: the site usage report carries Site Id but the only person on it is the OWNER; the Cloud Governance User Activity report logs console actions (Submit, Log in), not site access; the Groups export has no membership column and only 241 of 2,575 sites are group backed anyway. The one source that carries UserId AND SiteUrl on the same row is the UNIFIED AUDIT LOG (Purview, FileAccessed and PageViewed). UNVERIFIED in this tenant, and it is the next thing to test. (b) 180 days is the longest period Microsoft serves, so a user last active 200 days ago is indistinguishable from one who never used EDRMS. Questions 3 and 16.</t>
         </is>
       </c>
     </row>

--- a/EDRMS_Dashboard_Contents_2026-08-17.xlsx
+++ b/EDRMS_Dashboard_Contents_2026-08-17.xlsx
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>EDRMS users with recorded activity, last 180 days, by department</t>
+          <t>EDRMS users with recorded activity, last 180 days, by department, office or RM</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Departments in the list</t>
+          <t>Departments, offices and RMs in the list</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Total number of documents in EDRMS, by department</t>
+          <t>Total number of documents in EDRMS, by department, office or RM</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Departments in the list</t>
+          <t>Departments, offices and RMs in the list</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Total number of records declared in EDRMS, by department</t>
+          <t>Total number of records declared in EDRMS, by department, office or RM</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Departments with zero declarations</t>
+          <t>Departments, offices and RMs with zero declarations</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Total number of physical counterparts identified, by department</t>
+          <t>Total number of physical counterparts identified, by department, office or RM</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Departments in the list</t>
+          <t>Departments, offices and RMs in the list</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Total number of records due for disposal in the next 12 months, by department</t>
+          <t>Total number of records due for disposal in the next 12 months, by department, office or RM</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr"/>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Share of department</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Share of department</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Share of department</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Share of department</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Share of department</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">

--- a/EDRMS_Dashboard_Contents_2026-08-17.xlsx
+++ b/EDRMS_Dashboard_Contents_2026-08-17.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Verdict tally" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bank-wide Oversight'!$A$1:$J$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Department Insights'!$A$1:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bank-wide Oversight'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Department Insights'!$A$1:$J$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Institutional File Plan'!$A$1:$J$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Retention and Disposal'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Records and Archive Holdings'!$A$1:$J$16</definedName>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Documents declared</t>
+          <t>Share of records</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -2998,14 +2998,14 @@
           <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records" and the weekly scan</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -3015,14 +3015,10 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Declared records divided by documents held, per unit.</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>Waits on the scan for the denominator.</t>
-        </is>
-      </c>
+          <t>This unit's declared records divided by all declared records, times 100.</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="n">
@@ -3030,44 +3026,28 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Table column</t>
+          <t>Drill title</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Share of records</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>This unit's declared records divided by all declared records, times 100.</t>
-        </is>
-      </c>
+          <t>Total number of physical counterparts identified, by department, office or RM</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr"/>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr"/>
+      <c r="H49" s="10" t="inlineStr"/>
+      <c r="I49" s="10" t="inlineStr"/>
       <c r="J49" s="10" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customHeight="1">
@@ -3081,23 +3061,39 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Drill title</t>
+          <t>Drill stat</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Total number of physical counterparts identified, by department, office or RM</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr"/>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr"/>
-      <c r="H50" s="10" t="inlineStr"/>
-      <c r="I50" s="10" t="inlineStr"/>
+          <t>Physical counterparts</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical, grouped by department.</t>
+        </is>
+      </c>
       <c r="J50" s="10" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
@@ -3116,12 +3112,12 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Physical counterparts</t>
+          <t>Share of declared records</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>One declared record with a paper original.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -3141,7 +3137,7 @@
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Count HasPhysical, grouped by department.</t>
+          <t>Physical counterparts divided by declared records, times 100.</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr"/>
@@ -3162,12 +3158,12 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Share of declared records</t>
+          <t>Records declared</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+          <t>One declared record.</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -3182,12 +3178,12 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>ListId, ItemId</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>Physical counterparts divided by declared records, times 100.</t>
+          <t>COUNT(*) from public."Records", grouped by the site's department.</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr"/>
@@ -3208,12 +3204,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Records declared</t>
+          <t>Departments, offices and RMs in the list</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>One declared record.</t>
+          <t>One organisational unit appearing in the table.</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -3223,17 +3219,17 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
+          <t>Cloud Governance Workspace report</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>ListId, ItemId</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>COUNT(*) from public."Records", grouped by the site's department.</t>
+          <t>Count distinct Department over the compliant site list.</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr"/>
@@ -3249,17 +3245,17 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Departments, offices and RMs in the list</t>
+          <t>Department / office / RM</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>One organisational unit appearing in the table.</t>
+          <t>One organisational unit: a department (CSD), an office (BIOC) or a resident mission. One column holds all three and nothing says which type a code is.</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -3279,10 +3275,15 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>Count distinct Department over the compliant site list.</t>
-        </is>
-      </c>
-      <c r="J54" s="10" t="inlineStr"/>
+          <t>Group the compliant site list by Department.
+Do NOT use DRM Department: it is filled on all 1,032 rows and every row reads 'CGAdoption'. B-Department, Department22 and Division are empty on every row.</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>240 of 1,032 sites (23%) name SEVERAL departments in one cell, e.g. 'CWRD;SARD'. Counting under every department overstates the total by 26%; counting under the first named makes SARD vanish. RAC's call. Audit question 1. Separately, RM is unconfirmed: Resident Mission or Records Manager. Audit question 14.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="10" t="n">
@@ -3300,12 +3301,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Department / office / RM</t>
+          <t>Records with a counterpart</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>One organisational unit: a department (CSD), an office (BIOC) or a resident mission. One column holds all three and nothing says which type a code is.</t>
+          <t>One declared record that also exists on paper. Named for the RECORD, not the paper object, because that is what the row counts.</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -3315,23 +3316,22 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Cloud Governance Workspace report</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>HasPhysical, SiteUrl</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Group the compliant site list by Department.
-Do NOT use DRM Department: it is filled on all 1,032 rows and every row reads 'CGAdoption'. B-Department, Department22 and Division are empty on every row.</t>
+          <t>SELECT COUNT(*) FROM public."Records" WHERE "HasPhysical" IS TRUE, grouped by unit or site.</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>240 of 1,032 sites (23%) name SEVERAL departments in one cell, e.g. 'CWRD;SARD'. Counting under every department overstates the total by 26%; counting under the first named makes SARD vanish. RAC's call. Audit question 1. Separately, RM is unconfirmed: Resident Mission or Records Manager. Audit question 14.</t>
+          <t>Turned over to RAC is a DIFFERENT measure with no source: no system we can reach records a physical custody event. Audit question 6.</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Physical counterparts</t>
+          <t>Records declared</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>One declared record with a paper original.</t>
+          <t>One declared record.</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>ListId, ItemId</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Count HasPhysical, grouped by department.</t>
+          <t>COUNT(*) from public."Records", grouped by the site's department.</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr"/>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Records declared</t>
+          <t>Share of records with a counterpart</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>One declared record.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>ListId, ItemId</t>
+          <t>HasPhysical</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>COUNT(*) from public."Records", grouped by the site's department.</t>
+          <t>Records with a counterpart divided by records declared, times 100.</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr"/>
@@ -3433,44 +3433,28 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
+          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Table column</t>
+          <t>Drill title</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Share with counterpart</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Records with a counterpart divided by records declared, times 100.</t>
-        </is>
-      </c>
+          <t>Total number of records due for disposal in the next 12 months, by department, office or RM</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr"/>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr"/>
+      <c r="H58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="inlineStr"/>
       <c r="J58" s="10" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
@@ -3484,24 +3468,44 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Drill title</t>
+          <t>Drill stat</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Total number of records due for disposal in the next 12 months, by department, office or RM</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr"/>
-      <c r="H59" s="10" t="inlineStr"/>
-      <c r="I59" s="10" t="inlineStr"/>
-      <c r="J59" s="10" t="inlineStr"/>
+          <t>Due within 30 days</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>One record whose disposal date falls in the next 30 days.</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Count records due between now and now + 30 days.</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>The three windows must nest: 30 inside 90 inside 12 months.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="10" t="n">
@@ -3519,12 +3523,12 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Due within 30 days</t>
+          <t>Due within 90 days</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>One record whose disposal date falls in the next 30 days.</t>
+          <t>One record due in the next 90 days.</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -3544,14 +3548,10 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>Count records due between now and now + 30 days.</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>The three windows must nest: 30 inside 90 inside 12 months.</t>
-        </is>
-      </c>
+          <t>Count records due between now and now + 90 days.</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="10" t="n">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Due within 90 days</t>
+          <t>Due within 12 months</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>One record due in the next 90 days.</t>
+          <t>One record due in the next 12 months.</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>Count records due between now and now + 90 days.</t>
+          <t>Count records due between now and now + 12 months.</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr"/>
@@ -3610,17 +3610,17 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Due within 12 months</t>
+          <t>Department / office / RM</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>One record due in the next 12 months.</t>
+          <t>One organisational unit: a department (CSD), an office (BIOC) or a resident mission. One column holds all three and nothing says which type a code is.</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
@@ -3630,20 +3630,25 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
+          <t>Cloud Governance Workspace report</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>EDRMSDueDateForDisposal</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>Count records due between now and now + 12 months.</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr"/>
+          <t>Group the compliant site list by Department.
+Do NOT use DRM Department: it is filled on all 1,032 rows and every row reads 'CGAdoption'. B-Department, Department22 and Division are empty on every row.</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>240 of 1,032 sites (23%) name SEVERAL departments in one cell, e.g. 'CWRD;SARD'. Counting under every department overstates the total by 26%; counting under the first named makes SARD vanish. RAC's call. Audit question 1. Separately, RM is unconfirmed: Resident Mission or Records Manager. Audit question 14.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="10" t="n">
@@ -3661,12 +3666,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Department / office / RM</t>
+          <t>Records due within 12 months</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>One organisational unit: a department (CSD), an office (BIOC) or a resident mission. One column holds all three and nothing says which type a code is.</t>
+          <t>One record whose disposal date is inside the window.</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -3676,25 +3681,20 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Cloud Governance Workspace report</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>EDRMSDueDateForDisposal</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Group the compliant site list by Department.
-Do NOT use DRM Department: it is filled on all 1,032 rows and every row reads 'CGAdoption'. B-Department, Department22 and Division are empty on every row.</t>
-        </is>
-      </c>
-      <c r="J63" s="10" t="inlineStr">
-        <is>
-          <t>240 of 1,032 sites (23%) name SEVERAL departments in one cell, e.g. 'CWRD;SARD'. Counting under every department overstates the total by 26%; counting under the first named makes SARD vanish. RAC's call. Audit question 1. Separately, RM is unconfirmed: Resident Mission or Records Manager. Audit question 14.</t>
-        </is>
-      </c>
+          <t>Count by department.</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="10" t="n">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Records due</t>
+          <t>Next due date</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>One record whose disposal date is inside the window.</t>
+          <t>The earliest disposal date still ahead, for this unit.</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Count by department.</t>
+          <t>MIN(EDRMSDueDateForDisposal) where the date is in the future, per unit.</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr"/>
@@ -3758,12 +3758,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Next due date</t>
+          <t>With counterpart</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>The earliest disposal date still ahead, for this unit.</t>
+          <t>One record due for disposal that also has a paper original.</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -3778,64 +3778,18 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>EDRMSDueDateForDisposal</t>
+          <t>EDRMSDueDateForDisposal, HasPhysical</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>MIN(EDRMSDueDateForDisposal) where the date is in the future, per unit.</t>
+          <t>Count records due where HasPhysical is true.</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr"/>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>With counterpart</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>One record due for disposal that also has a paper original.</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal, HasPhysical</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Count records due where HasPhysical is true.</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J66"/>
+  <autoFilter ref="A1:J65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3846,7 +3800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6642,7 +6596,7 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Documents declared</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -6650,14 +6604,14 @@
           <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
-      <c r="F63" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records" and the weekly scan</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -6667,14 +6621,10 @@
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Declared records divided by documents held, per unit.</t>
-        </is>
-      </c>
-      <c r="J63" s="10" t="inlineStr">
-        <is>
-          <t>Waits on the scan for the denominator.</t>
-        </is>
-      </c>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="10" t="n">
@@ -6687,39 +6637,23 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Table column</t>
+          <t>Also asked for</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Share of department / office / RM</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>This row's figure divided by the department total, times 100.</t>
-        </is>
-      </c>
+          <t>Records declared month on month, and declaration rate per site</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr"/>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>Asked for, not built</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr"/>
+      <c r="H64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr"/>
       <c r="J64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1">
@@ -6738,19 +6672,39 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Records declared month on month, and declaration rate per site</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr"/>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr"/>
-      <c r="H65" s="10" t="inlineStr"/>
-      <c r="I65" s="10" t="inlineStr"/>
-      <c r="J65" s="10" t="inlineStr"/>
+          <t>Sites with no declared record in 90 days</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS site whose most recent declaration is older than 90 days.</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl, CreatedDate</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>MAX(CreatedDate) per SiteUrl, count the sites where it is older than 90 days.</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>A compliance finding: a site designated EDRMS that has stopped being used.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="10" t="n">
@@ -6758,49 +6712,29 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Also asked for</t>
+          <t>Drill title</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Sites with no declared record in 90 days</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>One EDRMS site whose most recent declaration is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>SiteUrl, CreatedDate</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>MAX(CreatedDate) per SiteUrl, count the sites where it is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
-        <is>
-          <t>A compliance finding: a site designated EDRMS that has stopped being used.</t>
-        </is>
-      </c>
+          <t>Physical counterpart</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr"/>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr"/>
+      <c r="H66" s="10" t="inlineStr"/>
+      <c r="I66" s="10" t="inlineStr"/>
+      <c r="J66" s="10" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="10" t="n">
@@ -6813,23 +6747,39 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Drill title</t>
+          <t>Drill stat</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Physical counterpart</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr"/>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr"/>
-      <c r="H67" s="10" t="inlineStr"/>
-      <c r="I67" s="10" t="inlineStr"/>
+          <t>Total number of physical records declared</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical, per site.</t>
+        </is>
+      </c>
       <c r="J67" s="10" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1">
@@ -6848,12 +6798,12 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Total number of physical records declared</t>
+          <t>Total number of users declaring records</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>One declared record with a paper original.</t>
+          <t>One person who declared at least one record here.</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
@@ -6868,15 +6818,19 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>CreatedBy</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>Count HasPhysical, per site.</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr"/>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>One line of SQL that has never been run.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="10" t="n">
@@ -6894,12 +6848,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Total number of users declaring records</t>
+          <t>Share of declared records</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>One person who declared at least one record here.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
@@ -6914,19 +6868,15 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>CreatedBy</t>
+          <t>HasPhysical</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr">
-        <is>
-          <t>One line of SQL that has never been run.</t>
-        </is>
-      </c>
+          <t>Physical counterparts divided by declared records, times 100.</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="10" t="n">
@@ -6944,12 +6894,12 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Share of declared records</t>
+          <t>Sites reporting</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+          <t>One site that appears in this table.</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -6959,17 +6909,17 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
+          <t>Cloud Governance Workspace report</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>EDRMS Site Type</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>Physical counterparts divided by declared records, times 100.</t>
+          <t>Count the rows in the table.</t>
         </is>
       </c>
       <c r="J70" s="10" t="inlineStr"/>
@@ -6985,17 +6935,17 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Sites reporting</t>
+          <t>Name of sites</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>One site that appears in this table.</t>
+          <t>One EDRMS SharePoint site.</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
@@ -7010,12 +6960,12 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>EDRMS Site Type</t>
+          <t>Workspace Name, URL</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>Count the rows in the table.</t>
+          <t>List the compliant sites for the selected unit.</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr"/>
@@ -7036,12 +6986,12 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Name of sites</t>
+          <t>Records with a counterpart</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>One EDRMS SharePoint site.</t>
+          <t>One declared record that also exists on paper. Named for the RECORD, not the paper object, because that is what the row counts.</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
@@ -7051,20 +7001,24 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Cloud Governance Workspace report</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Workspace Name, URL</t>
+          <t>HasPhysical, SiteUrl</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>List the compliant sites for the selected unit.</t>
-        </is>
-      </c>
-      <c r="J72" s="10" t="inlineStr"/>
+          <t>SELECT COUNT(*) FROM public."Records" WHERE "HasPhysical" IS TRUE, grouped by unit or site.</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Turned over to RAC is a DIFFERENT measure with no source: no system we can reach records a physical custody event. Audit question 6.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="10" t="n">
@@ -7082,12 +7036,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Total number of physical records declared</t>
+          <t>Total number of users declaring records</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>One declared record with a paper original.</t>
+          <t>One person who declared at least one record here.</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -7102,15 +7056,19 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>CreatedBy</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Count HasPhysical, per site.</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr"/>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>One line of SQL that has never been run.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="10" t="n">
@@ -7128,12 +7086,12 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Total number of users declaring records</t>
+          <t>Share of records with a counterpart</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>One person who declared at least one record here.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -7148,19 +7106,15 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>CreatedBy</t>
+          <t>HasPhysical</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>One line of SQL that has never been run.</t>
-        </is>
-      </c>
+          <t>Records with a counterpart divided by records declared, times 100.</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="10" t="n">
@@ -7178,7 +7132,7 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Share with a counterpart</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
@@ -7198,12 +7152,12 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Records with a counterpart divided by records declared, times 100.</t>
+          <t>This row's figure divided by the department total, times 100.</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr"/>
@@ -7219,39 +7173,23 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Table column</t>
+          <t>Also asked for</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Share of department / office / RM</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>This row's figure divided by the department total, times 100.</t>
-        </is>
-      </c>
+          <t>Physical records declared month on month, per department</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr"/>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>Asked for, not built</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr"/>
+      <c r="H76" s="10" t="inlineStr"/>
+      <c r="I76" s="10" t="inlineStr"/>
       <c r="J76" s="10" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
@@ -7270,7 +7208,7 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Physical records declared month on month, per department</t>
+          <t>Physical counterpart completion rate, records turned over for RAC storage against records declared with a counterpart</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr"/>
@@ -7290,23 +7228,23 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
+          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Also asked for</t>
+          <t>Drill title</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Physical counterpart completion rate, records turned over for RAC storage against records declared with a counterpart</t>
+          <t>Disposal</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr"/>
-      <c r="F78" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr"/>
@@ -7325,24 +7263,45 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Drill title</t>
+          <t>Drill stat</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Disposal</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr"/>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr"/>
-      <c r="H79" s="10" t="inlineStr"/>
-      <c r="I79" s="10" t="inlineStr"/>
-      <c r="J79" s="10" t="inlineStr"/>
+          <t>Total number of records due for disposal, next 12 months</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>One declared record whose disposal date falls inside the next 12 months.</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM public."Records"
+WHERE "EDRMSDueDateForDisposal" BETWEEN now() AND now() + interval '12 months'</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>Records DISPOSED needs a disposal status the application does not have. Audit question 7.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="10" t="n">
@@ -7360,12 +7319,12 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Total number of records due for disposal, next 12 months</t>
+          <t>Libraries with records due</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>One declared record whose disposal date falls inside the next 12 months.</t>
+          <t>One library holding at least one record due for disposal.</t>
         </is>
       </c>
       <c r="F80" s="13" t="inlineStr">
@@ -7380,20 +7339,15 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>EDRMSDueDateForDisposal</t>
+          <t>ListId, EDRMSDueDateForDisposal</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM public."Records"
-WHERE "EDRMSDueDateForDisposal" BETWEEN now() AND now() + interval '12 months'</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>Records DISPOSED needs a disposal status the application does not have. Audit question 7.</t>
-        </is>
-      </c>
+          <t>Count distinct ListId among records due.</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="10" t="n">
@@ -7406,17 +7360,17 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Libraries with records due</t>
+          <t>Library name</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>One library holding at least one record due for disposal.</t>
+          <t>One document library inside an EDRMS site.</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -7426,20 +7380,24 @@
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>ListId, EDRMSDueDateForDisposal</t>
+          <t>drives, list.id</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Count distinct ListId among records due.</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr"/>
+          <t>GET /sites/{siteId}/drives. list.id is the ListId key that joins to Records.</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Always show a library with its parent site: display names repeat across sites.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="10" t="n">
@@ -7457,12 +7415,12 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Library name</t>
+          <t>Number of records due for disposal</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>One document library inside an EDRMS site.</t>
+          <t>One record due in the window.</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
@@ -7472,24 +7430,20 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>drives, list.id</t>
+          <t>EDRMSDueDateForDisposal</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>GET /sites/{siteId}/drives. list.id is the ListId key that joins to Records.</t>
-        </is>
-      </c>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>Always show a library with its parent site: display names repeat across sites.</t>
-        </is>
-      </c>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="10" t="n">
@@ -7507,12 +7461,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Number of records due for disposal</t>
+          <t>Next due date for disposal</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>One record due in the window.</t>
+          <t>The earliest disposal date still ahead for this library.</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -7532,7 +7486,7 @@
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Count records due, per site or library.</t>
+          <t>MIN(EDRMSDueDateForDisposal) in the future, per ListId.</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr"/>
@@ -7553,12 +7507,12 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Next due date for disposal</t>
+          <t>With physical counterpart?</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>The earliest disposal date still ahead for this library.</t>
+          <t>Whether the records due here include paper originals.</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
@@ -7573,12 +7527,12 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>EDRMSDueDateForDisposal</t>
+          <t>HasPhysical</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>MIN(EDRMSDueDateForDisposal) in the future, per ListId.</t>
+          <t>Any HasPhysical among the library's records due.</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr"/>
@@ -7599,12 +7553,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>With physical counterpart?</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Whether the records due here include paper originals.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -7619,12 +7573,12 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>HasPhysical</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Any HasPhysical among the library's records due.</t>
+          <t>This row's figure divided by the department total, times 100.</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr"/>
@@ -7640,39 +7594,23 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Table column</t>
+          <t>Also asked for</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Share of department / office / RM</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>This row's figure divided by the department total, times 100.</t>
-        </is>
-      </c>
+          <t>Records disposed month on month, per department and division</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr"/>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>Asked for, not built</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr"/>
+      <c r="H86" s="10" t="inlineStr"/>
+      <c r="I86" s="10" t="inlineStr"/>
       <c r="J86" s="10" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1">
@@ -7691,7 +7629,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Records disposed month on month, per department and division</t>
+          <t>Overdue disposal actions and pending approvals</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr"/>
@@ -7721,7 +7659,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Overdue disposal actions and pending approvals</t>
+          <t>Disposal completion rate, including physical counterparts</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr"/>
@@ -7751,7 +7689,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Disposal completion rate, including physical counterparts</t>
+          <t>Records due next quarter, for planning and advance notice</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr"/>
@@ -7765,38 +7703,8 @@
       <c r="I89" s="10" t="inlineStr"/>
       <c r="J89" s="10" t="inlineStr"/>
     </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>Records due next quarter, for planning and advance notice</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr"/>
-      <c r="F90" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr"/>
-      <c r="H90" s="10" t="inlineStr"/>
-      <c r="I90" s="10" t="inlineStr"/>
-      <c r="J90" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:J89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11156,7 +11064,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -11196,7 +11104,7 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/EDRMS_Dashboard_Contents_2026-08-17.xlsx
+++ b/EDRMS_Dashboard_Contents_2026-08-17.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bank-wide Oversight'!$A$1:$J$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Department Insights'!$A$1:$J$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Department Insights'!$A$1:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Institutional File Plan'!$A$1:$J$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Retention and Disposal'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Records and Archive Holdings'!$A$1:$J$16</definedName>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Total number of records due for disposal, next 12 months</t>
+          <t>Total number of records due for disposal within 12 months</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Records due for disposal, next 12 months</t>
+          <t>Records due for disposal within 12 months</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Total number of records due for disposal in the next 12 months, by department, office or RM</t>
+          <t>Total number of records due for disposal within 12 months, by department, office or RM</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Total number of records due for disposal, next 12 months</t>
+          <t>Total number of records due for disposal within 12 months</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Total number of sites created</t>
+          <t>Name of sites</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>One EDRMS site owned by this unit.</t>
+          <t>One EDRMS SharePoint site.</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -4403,21 +4403,17 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>EDRMS Site Type, Department</t>
+          <t>Workspace Name, URL</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Count compliant sites for the unit.</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Same multi-department problem. Audit question 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+          <t>List the compliant sites for the selected unit.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>14</v>
       </c>
@@ -4428,35 +4424,705 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
+          <t>Site owners</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>The person accountable for the site.</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Primary Business Owner</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Read Primary Business Owner per site.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Populated on 100% of Cloud Governance rows. The M365 export had 19 sites with no owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of sites created"</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Number of documents</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>One document held by this site.</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>The weekly scan</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Count documents in the site's libraries.</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of sites created"</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Number of records</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>One declared record.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>ListId, ItemId</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>COUNT(*) FROM public."Records"</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of sites created"</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Number of physical counterparts</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>One declared record with a paper original.</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>HasPhysical, SiteUrl</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Count HasPhysical per site.</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of sites created"</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Number of records due for disposal</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>One record due in the window.</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>EDRMSDueDateForDisposal</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of EDRMS users"</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Drill title</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of EDRMS users"</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>An activity band, not a measure: the row label for the users table.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of EDRMS users"</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Number of users</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>One person in this activity band.</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Needs the client</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint activity user detail (M365)</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Last Activity Date</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Count users falling in the band.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Needs the user to department mapping. Audit question 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of EDRMS users"</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Share of department / office / RM</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of site visitors"</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Drill title</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Visitors</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of site visitors"</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Name of sites</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS SharePoint site.</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Workspace Name, URL</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>List the compliant sites for the selected unit.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of site visitors"</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Total number of visitors</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>One PERSON who opened a site. A person visiting fifty times is ONE visitor.</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft Graph site analytics</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>actorCount</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>GET /sites/{siteId}/analytics/allTime, read actorCount, per site.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Graph offers allTime and lastSevenDays ONLY. There is no 30 day unique viewer figure, however often it is asked for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of site visitors"</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Page views</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>One EVENT. Fifty visits by one person are fifty page views.</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint site usage detail (M365)</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Page View Count</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Sum Page View Count per site, then group by the site's department.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Page views and visitors are two measures. They must never be shown as one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of site visitors"</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Views per visitor</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>A RATE: page views over visitors, for the same site.</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>SharePoint site usage detail (M365) and Graph analytics</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Page View Count, actorCount</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Page views divided by visitors, per site.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the visitor figure, which needs a per site Graph call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of site visitors"</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Table column</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Share of department / office / RM</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Drill behind "Total number of documents in EDRMS"</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Drill title</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
           <t>Total number of documents in EDRMS</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>One document held in an EDRMS site, declared or not.</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>Needs the weekly scan</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>The weekly scan, not yet built</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>1. Take the compliant site list from the Workspace report.
 2. For each site, walk its libraries through Microsoft Graph.
@@ -4464,680 +5130,9 @@
 INTERIM: sum File Count from the site usage export, joined on Site Id.</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>The weekly scan is the single biggest self-help item left, and needs nobody else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Total number of records declared in EDRMS</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>One declared record. The table holds NO ROW for an undeclared document.</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>ListId, ItemId</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM public."Records"</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Total number of physical counterparts identified</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>One declared record that also exists on paper.</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM public."Records" WHERE "HasPhysical" IS TRUE</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Turned over to RAC is a DIFFERENT measure and has no source: no system records a physical custody event. Audit question 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Total number of records due for disposal, next 12 months</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>One declared record whose disposal date falls inside the next 12 months.</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM public."Records"
-WHERE "EDRMSDueDateForDisposal" BETWEEN now() AND now() + interval '12 months'</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Records DISPOSED needs a disposal status the application does not have. Audit question 7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Name of sites</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>One EDRMS SharePoint site.</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Workspace Name, URL</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>List the compliant sites for the selected unit.</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Site owners</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>The person accountable for the site.</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Primary Business Owner</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Read Primary Business Owner per site.</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Populated on 100% of Cloud Governance rows. The M365 export had 19 sites with no owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Number of documents</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>One document held by this site.</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>The weekly scan</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Count documents in the site's libraries.</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Waits on the scan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Number of records</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>One declared record.</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>ListId, ItemId</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>COUNT(*) FROM public."Records"</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Number of physical counterparts</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>One declared record with a paper original.</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical, SiteUrl</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Count HasPhysical per site.</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>Number of records due for disposal</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>One record due in the window.</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Count records due, per site or library.</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Sites with no activity in 90 days: 73</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of sites created"</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Records declared month on month, per department and division</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Drill title</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Users with recorded activity</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>One person with activity in the window. NOT a site and NOT a visit.</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Needs the client</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>SharePoint activity user detail (M365)</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>User Principal Name</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Count distinct User Principal Name with activity inside the window.</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>No site dimension, so it cannot be narrowed to EDRMS. Audit question 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Never accessed EDRMS</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>One licensed person with no recorded activity at all.</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>Needs the client</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>SharePoint activity user detail (M365)</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Last Activity Date</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Count rows where Last Activity Date is blank.</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>Indistinguishable from 'last active more than 180 days ago', because 180 is the longest period the report serves. Audit question 16.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>No access in 90 days</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>One person whose last activity is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Needs the client</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>SharePoint activity user detail (M365)</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Last Activity Date</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Count rows where Last Activity Date is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>Same as above, plus the EDRMS narrowing problem. Audit question 3.</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5142,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
+          <t>Drill behind "Total number of documents in EDRMS"</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -5157,22 +5152,34 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Name of sites</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>An activity band, not a measure: the row label for the users table.</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
+          <t>One EDRMS SharePoint site.</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Workspace Name, URL</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>List the compliant sites for the selected unit.</t>
+        </is>
+      </c>
       <c r="J31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -5181,7 +5188,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
+          <t>Drill behind "Total number of documents in EDRMS"</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -5191,37 +5198,37 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Number of users</t>
+          <t>Number of documents created / uploaded</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>One person in this activity band.</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Needs the client</t>
+          <t>One document created or uploaded here.</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>SharePoint activity user detail (M365)</t>
+          <t>The weekly scan</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>Last Activity Date</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>Count users falling in the band.</t>
+          <t>Count documents per site.</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>Needs the user to department mapping. Audit question 3.</t>
+          <t>Nothing marks a document as MIGRATED, so migrated counts cannot be split out. Question 9.</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5238,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
+          <t>Drill behind "Total number of documents in EDRMS"</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -5241,35 +5248,39 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Share of department / office / RM</t>
+          <t>Number of users creating documents</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
+          <t>One person who created a document here.</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Needs the weekly scan</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
+          <t>The weekly scan</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CreatedBy</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>This row's figure divided by the department total, times 100.</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr"/>
+          <t>Count distinct document authors per site.</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Waits on the scan.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="10" t="n">
@@ -5277,28 +5288,44 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
+          <t>Drill behind "Total number of documents in EDRMS"</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Also asked for</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Active users month on month, per department</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr"/>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr"/>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="10" t="inlineStr"/>
+          <t>Documents size (in GB)</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Bytes held by this site.</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Storage Used (GB)</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Read Storage Used (GB) per site.</t>
+        </is>
+      </c>
       <c r="J34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -5307,23 +5334,23 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
+          <t>Drill behind "Total number of records declared in EDRMS"</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Also asked for</t>
+          <t>Drill title</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Users who have not accessed their site, to track transfers and leavers</t>
+          <t>Compliance review, record declaration</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
@@ -5337,59 +5364,97 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of EDRMS users"</t>
+          <t>Drill behind "Total number of records declared in EDRMS"</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Also asked for</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>New users, listed for onboarding</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr"/>
-      <c r="I36" s="10" t="inlineStr"/>
+          <t>Name of sites</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>One EDRMS SharePoint site.</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Cloud Governance Workspace report</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Workspace Name, URL</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>List the compliant sites for the selected unit.</t>
+        </is>
+      </c>
       <c r="J36" s="10" t="inlineStr"/>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="10" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of records declared in EDRMS"</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Drill title</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Visitors</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr"/>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
+          <t>Total number of records declared</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>One declared record in this unit's sites.</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>drm-npr PostgreSQL, public."Records"</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>SiteUrl</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>1. SELECT "SiteUrl", COUNT(*) FROM public."Records" GROUP BY "SiteUrl"
+2. Join SiteUrl to the Workspace report's URL.
+3. Group by that report's Department.</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Same multi-department problem. Audit question 1.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="10" t="n">
@@ -5397,47 +5462,47 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of records declared in EDRMS"</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Total number of visitors</t>
+          <t>People who declared a record</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>One PERSON who opened a site. A person visiting fifty times is ONE visitor.</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+          <t>One person who declared at least one record. NOT a record and NOT a document.</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Microsoft Graph site analytics</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>actorCount</t>
+          <t>CreatedBy</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>GET /sites/{siteId}/analytics/allTime, read actorCount, per site.</t>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records"</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>Graph offers allTime and lastSevenDays ONLY. There is no 30 day unique viewer figure, however often it is asked for.</t>
+          <t>One line of SQL that has never been run. Until it is, the prototype shows demo data here. This is the cheapest real number left in the project.</t>
         </is>
       </c>
     </row>
@@ -5447,22 +5512,22 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of records declared in EDRMS"</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Page views</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>One EVENT. Fifty visits by one person are fifty page views.</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -5472,24 +5537,20 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>SharePoint site usage detail (M365)</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Page View Count</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>Sum Page View Count per site, then group by the site's department.</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>Page views and visitors are two measures. They must never be shown as one.</t>
-        </is>
-      </c>
+          <t>This row's figure divided by the department total, times 100.</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="10" t="n">
@@ -5497,44 +5558,28 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Drill title</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Sites reporting</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>One site that appears in this table.</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS Site Type</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Count the rows in the table.</t>
-        </is>
-      </c>
+          <t>Physical counterpart</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr"/>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="inlineStr"/>
       <c r="J40" s="10" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -5543,7 +5588,7 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -5589,7 +5634,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -5599,37 +5644,37 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Total number of visitors</t>
+          <t>Records with a counterpart</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>One PERSON who opened a site. A person visiting fifty times is ONE visitor.</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+          <t>One declared record that also exists on paper. Named for the RECORD, not the paper object, because that is what the row counts.</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Microsoft Graph site analytics</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>actorCount</t>
+          <t>HasPhysical, SiteUrl</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>GET /sites/{siteId}/analytics/allTime, read actorCount, per site.</t>
+          <t>SELECT COUNT(*) FROM public."Records" WHERE "HasPhysical" IS TRUE, grouped by unit or site.</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>Graph offers allTime and lastSevenDays ONLY. There is no 30 day unique viewer figure, however often it is asked for.</t>
+          <t>Turned over to RAC is a DIFFERENT measure with no source: no system we can reach records a physical custody event. Audit question 6.</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5684,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -5649,12 +5694,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Page views</t>
+          <t>Total number of users declaring records</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>One EVENT. Fifty visits by one person are fifty page views.</t>
+          <t>One person who declared at least one record here.</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -5664,22 +5709,22 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>SharePoint site usage detail (M365)</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Page View Count</t>
+          <t>CreatedBy</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Sum Page View Count per site, then group by the site's department.</t>
+          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Page views and visitors are two measures. They must never be shown as one.</t>
+          <t>One line of SQL that has never been run.</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5734,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -5699,39 +5744,35 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Views per visitor</t>
+          <t>Share of records with a counterpart</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>A RATE: page views over visitors, for the same site.</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>SharePoint site usage detail (M365) and Graph analytics</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Page View Count, actorCount</t>
+          <t>HasPhysical</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>Page views divided by visitors, per site.</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>Waits on the visitor figure, which needs a per site Graph call.</t>
-        </is>
-      </c>
+          <t>Records with a counterpart divided by records declared, times 100.</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="10" t="n">
@@ -5739,7 +5780,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of site visitors"</t>
+          <t>Drill behind "Total number of physical counterparts identified"</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -5779,13 +5820,13 @@
       </c>
       <c r="J45" s="10" t="inlineStr"/>
     </row>
-    <row r="46" ht="48" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="10" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -5795,42 +5836,19 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Total number of documents in EDRMS</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>One document held in an EDRMS site, declared or not.</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>The weekly scan, not yet built</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>1. Take the compliant site list from the Workspace report.
-2. For each site, walk its libraries through Microsoft Graph.
-3. Count items that are files, not folders.
-INTERIM: sum File Count from the site usage export, joined on Site Id.</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>The weekly scan is the single biggest self-help item left, and needs nobody else.</t>
-        </is>
-      </c>
+          <t>Disposal</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Not a measure</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr"/>
+      <c r="H46" s="10" t="inlineStr"/>
+      <c r="I46" s="10" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="10" t="n">
@@ -5838,47 +5856,47 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Total number of documents</t>
+          <t>Library name</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>One document in this unit's sites.</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+          <t>One document library inside an EDRMS site.</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>The weekly scan</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>drives, list.id</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Sum the document count over the unit's sites.</t>
+          <t>GET /sites/{siteId}/drives. list.id is the ListId key that joins to Records.</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Waits on the scan.</t>
+          <t>Always show a library with its parent site: display names repeat across sites.</t>
         </is>
       </c>
     </row>
@@ -5888,22 +5906,22 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Total documents size</t>
+          <t>Number of records due for disposal</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>Bytes held by this unit's documents.</t>
+          <t>One record due in the window.</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -5913,24 +5931,20 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Cloud Governance Workspace report</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Storage Used (GB)</t>
+          <t>EDRMSDueDateForDisposal</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Sum Storage Used (GB) over the unit's sites.</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>Never inferred from a document count.</t>
-        </is>
-      </c>
+          <t>Count records due, per site or library.</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="10" t="n">
@@ -5938,22 +5952,22 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Drill stat</t>
+          <t>Table column</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Sites reporting</t>
+          <t>Next due date for disposal</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>One site that appears in this table.</t>
+          <t>The earliest disposal date still ahead for this library.</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -5963,17 +5977,17 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Cloud Governance Workspace report</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>EDRMS Site Type</t>
+          <t>EDRMSDueDateForDisposal</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Count the rows in the table.</t>
+          <t>MIN(EDRMSDueDateForDisposal) in the future, per ListId.</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr"/>
@@ -5984,7 +5998,7 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -5994,12 +6008,12 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Name of sites</t>
+          <t>With physical counterpart?</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>One EDRMS SharePoint site.</t>
+          <t>Whether the records due here include paper originals.</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -6009,17 +6023,17 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Cloud Governance Workspace report</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Workspace Name, URL</t>
+          <t>HasPhysical</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>List the compliant sites for the selected unit.</t>
+          <t>Any HasPhysical among the library's records due.</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr"/>
@@ -6030,7 +6044,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
+          <t>Drill behind "Total number of records due for disposal within 12 months"</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -6040,22 +6054,22 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Number of documents created / uploaded</t>
+          <t>Share of department / office / RM</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>One document created or uploaded here.</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
+          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>Ready</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>The weekly scan</t>
+          <t>drm-npr PostgreSQL, public."Records"</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -6065,1646 +6079,13 @@
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Count documents per site.</t>
-        </is>
-      </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>Nothing marks a document as MIGRATED, so migrated counts cannot be split out. Question 9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Number of users creating documents</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>One person who created a document here.</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>The weekly scan</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>Count distinct document authors per site.</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>Waits on the scan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Documents size (in GB)</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>Bytes held by this site.</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>Storage Used (GB)</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>Read Storage Used (GB) per site.</t>
-        </is>
-      </c>
-      <c r="J53" s="10" t="inlineStr"/>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of documents in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>New documents created month on month, per department and division</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr"/>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr"/>
-      <c r="H54" s="10" t="inlineStr"/>
-      <c r="I54" s="10" t="inlineStr"/>
-      <c r="J54" s="10" t="inlineStr"/>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>Drill title</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>Compliance review, record declaration</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr"/>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="10" t="inlineStr"/>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>Total number of records declared</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>One declared record in this unit's sites.</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>SiteUrl</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>1. SELECT "SiteUrl", COUNT(*) FROM public."Records" GROUP BY "SiteUrl"
-2. Join SiteUrl to the Workspace report's URL.
-3. Group by that report's Department.</t>
-        </is>
-      </c>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t>Same multi-department problem. Audit question 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>Total number of users declaring records</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>One person who declared at least one record here.</t>
-        </is>
-      </c>
-      <c r="F57" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
-        </is>
-      </c>
-      <c r="J57" s="10" t="inlineStr">
-        <is>
-          <t>One line of SQL that has never been run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>Total declared record size</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>Bytes held by the declared records specifically.</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>Needs the weekly scan</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>The weekly scan</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>FileSize</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Sum FileSize over the documents that appear in Records.</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>Graph returns a CUMULATIVE size on folders, so the scan must filter to files only or storage is double counted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>Sites with no declared record in 90 days</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>One EDRMS site whose most recent declaration is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>SiteUrl, CreatedDate</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>MAX(CreatedDate) per SiteUrl, count the sites where it is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>A compliance finding: a site designated EDRMS that has stopped being used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>Name of sites</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>One EDRMS SharePoint site.</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>Workspace Name, URL</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>List the compliant sites for the selected unit.</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr"/>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>Total number of records declared</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>One declared record in this unit's sites.</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>SiteUrl</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>1. SELECT "SiteUrl", COUNT(*) FROM public."Records" GROUP BY "SiteUrl"
-2. Join SiteUrl to the Workspace report's URL.
-3. Group by that report's Department.</t>
-        </is>
-      </c>
-      <c r="J61" s="10" t="inlineStr">
-        <is>
-          <t>Same multi-department problem. Audit question 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>People who declared a record</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>One person who declared at least one record. NOT a record and NOT a document.</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records"</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>One line of SQL that has never been run. Until it is, the prototype shows demo data here. This is the cheapest real number left in the project.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>Share of department / office / RM</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
           <t>This row's figure divided by the department total, times 100.</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr"/>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>Records declared month on month, and declaration rate per site</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr"/>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr"/>
-      <c r="H64" s="10" t="inlineStr"/>
-      <c r="I64" s="10" t="inlineStr"/>
-      <c r="J64" s="10" t="inlineStr"/>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records declared in EDRMS"</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>Sites with no declared record in 90 days</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>One EDRMS site whose most recent declaration is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>SiteUrl, CreatedDate</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>MAX(CreatedDate) per SiteUrl, count the sites where it is older than 90 days.</t>
-        </is>
-      </c>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>A compliance finding: a site designated EDRMS that has stopped being used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>Drill title</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>Physical counterpart</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr"/>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr"/>
-      <c r="H66" s="10" t="inlineStr"/>
-      <c r="I66" s="10" t="inlineStr"/>
-      <c r="J66" s="10" t="inlineStr"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>Total number of physical records declared</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>One declared record with a paper original.</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical</t>
-        </is>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>Count HasPhysical, per site.</t>
-        </is>
-      </c>
-      <c r="J67" s="10" t="inlineStr"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>Total number of users declaring records</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>One person who declared at least one record here.</t>
-        </is>
-      </c>
-      <c r="F68" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>One line of SQL that has never been run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>Share of declared records</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>Physical counterparts divided by declared records, times 100.</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>Sites reporting</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>One site that appears in this table.</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>EDRMS Site Type</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Count the rows in the table.</t>
-        </is>
-      </c>
-      <c r="J70" s="10" t="inlineStr"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>Name of sites</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>One EDRMS SharePoint site.</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>Cloud Governance Workspace report</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Workspace Name, URL</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>List the compliant sites for the selected unit.</t>
-        </is>
-      </c>
-      <c r="J71" s="10" t="inlineStr"/>
-    </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>Records with a counterpart</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>One declared record that also exists on paper. Named for the RECORD, not the paper object, because that is what the row counts.</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical, SiteUrl</t>
-        </is>
-      </c>
-      <c r="I72" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM public."Records" WHERE "HasPhysical" IS TRUE, grouped by unit or site.</t>
-        </is>
-      </c>
-      <c r="J72" s="10" t="inlineStr">
-        <is>
-          <t>Turned over to RAC is a DIFFERENT measure with no source: no system we can reach records a physical custody event. Audit question 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>Total number of users declaring records</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>One person who declared at least one record here.</t>
-        </is>
-      </c>
-      <c r="F73" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>CreatedBy</t>
-        </is>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(DISTINCT "CreatedBy") FROM public."Records", per unit.</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr">
-        <is>
-          <t>One line of SQL that has never been run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>Share of records with a counterpart</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Records with a counterpart divided by records declared, times 100.</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr"/>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>Share of department / office / RM</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F75" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>This row's figure divided by the department total, times 100.</t>
-        </is>
-      </c>
-      <c r="J75" s="10" t="inlineStr"/>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>Physical records declared month on month, per department</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr"/>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr"/>
-      <c r="H76" s="10" t="inlineStr"/>
-      <c r="I76" s="10" t="inlineStr"/>
-      <c r="J76" s="10" t="inlineStr"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of physical counterparts identified"</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>Physical counterpart completion rate, records turned over for RAC storage against records declared with a counterpart</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr"/>
-      <c r="F77" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr"/>
-      <c r="H77" s="10" t="inlineStr"/>
-      <c r="I77" s="10" t="inlineStr"/>
-      <c r="J77" s="10" t="inlineStr"/>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>Drill title</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>Disposal</t>
-        </is>
-      </c>
-      <c r="E78" s="10" t="inlineStr"/>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>Not a measure</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr"/>
-      <c r="H78" s="10" t="inlineStr"/>
-      <c r="I78" s="10" t="inlineStr"/>
-      <c r="J78" s="10" t="inlineStr"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>Total number of records due for disposal, next 12 months</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>One declared record whose disposal date falls inside the next 12 months.</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM public."Records"
-WHERE "EDRMSDueDateForDisposal" BETWEEN now() AND now() + interval '12 months'</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>Records DISPOSED needs a disposal status the application does not have. Audit question 7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="10" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>Drill stat</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>Libraries with records due</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>One library holding at least one record due for disposal.</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>ListId, EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Count distinct ListId among records due.</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr"/>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>Library name</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>One document library inside an EDRMS site.</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
-        <is>
-          <t>Microsoft Graph</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>drives, list.id</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>GET /sites/{siteId}/drives. list.id is the ListId key that joins to Records.</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>Always show a library with its parent site: display names repeat across sites.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>Number of records due for disposal</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>One record due in the window.</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>Count records due, per site or library.</t>
-        </is>
-      </c>
-      <c r="J82" s="10" t="inlineStr"/>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>Next due date for disposal</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>The earliest disposal date still ahead for this library.</t>
-        </is>
-      </c>
-      <c r="F83" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>EDRMSDueDateForDisposal</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>MIN(EDRMSDueDateForDisposal) in the future, per ListId.</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr"/>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>With physical counterpart?</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>Whether the records due here include paper originals.</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>HasPhysical</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Any HasPhysical among the library's records due.</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr"/>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Table column</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>Share of department / office / RM</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>A RATE, not a count. Arithmetic on two figures already on this row.</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>drm-npr PostgreSQL, public."Records"</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>This row's figure divided by the department total, times 100.</t>
-        </is>
-      </c>
-      <c r="J85" s="10" t="inlineStr"/>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>Records disposed month on month, per department and division</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr"/>
-      <c r="F86" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr"/>
-      <c r="H86" s="10" t="inlineStr"/>
-      <c r="I86" s="10" t="inlineStr"/>
-      <c r="J86" s="10" t="inlineStr"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="10" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>Overdue disposal actions and pending approvals</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr"/>
-      <c r="H87" s="10" t="inlineStr"/>
-      <c r="I87" s="10" t="inlineStr"/>
-      <c r="J87" s="10" t="inlineStr"/>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>Disposal completion rate, including physical counterparts</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr"/>
-      <c r="F88" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr"/>
-      <c r="H88" s="10" t="inlineStr"/>
-      <c r="I88" s="10" t="inlineStr"/>
-      <c r="J88" s="10" t="inlineStr"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>Drill behind "Total number of records due for disposal, next 12 months"</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>Also asked for</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>Records due next quarter, for planning and advance notice</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr"/>
-      <c r="F89" s="16" t="inlineStr">
-        <is>
-          <t>Asked for, not built</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr"/>
-      <c r="H89" s="10" t="inlineStr"/>
-      <c r="I89" s="10" t="inlineStr"/>
-      <c r="J89" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J89"/>
+  <autoFilter ref="A1:J51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11054,7 +9435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -11064,7 +9445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -11074,7 +9455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -11084,7 +9465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -11104,7 +9485,7 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>231</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
